--- a/currensies_test.xlsx
+++ b/currensies_test.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">شيكل</t>
   </si>
   <si>
-    <t xml:space="preserve">ش</t>
+    <t xml:space="preserve">₪</t>
   </si>
 </sst>
 </file>
@@ -64,7 +64,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -105,6 +105,11 @@
       <name val="Noto Sans Devanagari"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -149,7 +154,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -183,6 +188,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -376,7 +385,7 @@
       <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="7"/>

--- a/currensies_test.xlsx
+++ b/currensies_test.xlsx
@@ -110,6 +110,7 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
